--- a/docs/workbook-split/dateien/Projektakte.xlsx
+++ b/docs/workbook-split/dateien/Projektakte.xlsx
@@ -575,13 +575,15 @@
       </c>
       <c r="D5" s="1" t="n"/>
       <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1">
-        <f>'[Steuerung.xlsx]Steuerung'!$F$10</f>
-        <v/>
-      </c>
-      <c r="G5" s="1">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$B$661:$B$828,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$C$661:$C$828,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$661:$B$828,0)))</f>
-        <v/>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>P4102608263</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>RB Föderbrücke AFB 60</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -634,9 +636,10 @@
           <t>Region</t>
         </is>
       </c>
-      <c r="D8" s="1">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$B$661:$B$828,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$L$661:$L$828,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$661:$B$828,0)))</f>
-        <v/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Ost</t>
+        </is>
       </c>
       <c r="E8" s="1" t="n"/>
       <c r="F8" s="1" t="n"/>
@@ -647,9 +650,8 @@
       </c>
       <c r="H8" s="1" t="n"/>
       <c r="I8" s="1" t="n"/>
-      <c r="J8" s="6">
-        <f>SUMIFS('[Risiken.xlsx]Risiken'!$N$7:$N$2271,'[Risiken.xlsx]Risiken'!$D$7:$D$2271,'[Steuerung.xlsx]Steuerung'!$F$10)</f>
-        <v/>
+      <c r="J8" s="6" t="n">
+        <v>2114974.43</v>
       </c>
       <c r="K8" s="1" t="n"/>
       <c r="L8" s="1" t="n"/>
@@ -665,9 +667,10 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="D9" s="1">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$B$661:$B$828,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$E$661:$E$828,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$661:$B$828,0)))</f>
-        <v/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>AKTIV</t>
+        </is>
       </c>
       <c r="E9" s="1" t="n"/>
       <c r="F9" s="1" t="n"/>
@@ -689,9 +692,8 @@
           <t>Leistung</t>
         </is>
       </c>
-      <c r="D10" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D10" s="7" t="n">
+        <v>2991108.78</v>
       </c>
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="n"/>
@@ -717,9 +719,8 @@
           <t>Variable Kosten</t>
         </is>
       </c>
-      <c r="D11" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$H$8:$H$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D11" s="7" t="n">
+        <v>2194487.29</v>
       </c>
       <c r="E11" s="1" t="n"/>
       <c r="F11" s="1" t="n"/>
@@ -733,9 +734,8 @@
           <t>Fixe Projektkosten</t>
         </is>
       </c>
-      <c r="D12" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$I$8:$I$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D12" s="7" t="n">
+        <v>530.27</v>
       </c>
       <c r="E12" s="1" t="n"/>
       <c r="F12" s="1" t="n"/>
@@ -748,9 +748,8 @@
           <t>Verrechnete Gemeinkosten</t>
         </is>
       </c>
-      <c r="D13" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$J$8:$J$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D13" s="7" t="n">
+        <v>27069.08</v>
       </c>
       <c r="E13" s="1" t="n"/>
       <c r="F13" s="1" t="n"/>
@@ -763,9 +762,8 @@
           <t>DB1</t>
         </is>
       </c>
-      <c r="D14" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D14" s="7" t="n">
+        <v>796621.49</v>
       </c>
       <c r="E14" s="1" t="n"/>
       <c r="F14" s="1" t="n"/>
@@ -778,9 +776,8 @@
           <t>DB2</t>
         </is>
       </c>
-      <c r="D15" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$P$8:$P$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D15" s="7" t="n">
+        <v>796091.22</v>
       </c>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="n"/>
@@ -793,9 +790,8 @@
           <t>DB3</t>
         </is>
       </c>
-      <c r="D16" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D16" s="7" t="n">
+        <v>769022.14</v>
       </c>
       <c r="E16" s="1" t="n"/>
       <c r="F16" s="1" t="n"/>
@@ -817,9 +813,8 @@
           <t>DB4</t>
         </is>
       </c>
-      <c r="D17" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,0)))</f>
-        <v/>
+      <c r="D17" s="7" t="n">
+        <v>659679.64</v>
       </c>
       <c r="E17" s="1" t="n"/>
       <c r="F17" s="1" t="n"/>
@@ -845,15 +840,15 @@
           <t>Budget Umsatz</t>
         </is>
       </c>
-      <c r="D18" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$B$661:$B$828,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$H$661:$H$828,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$661:$B$828,0)))</f>
-        <v/>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="n"/>
       <c r="F18" s="1" t="n"/>
-      <c r="G18" s="1">
-        <f>IF(L17="","Kommentar mit Projekt-Nr. kennzeichnen",IF(L17='[Steuerung.xlsx]Steuerung'!$F$10,"Kommentar zu ausgewähltem Projekt","Kommentar gehört zu anderem Projekt"))</f>
-        <v/>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>Kommentar mit Projekt-Nr. kennzeichnen</t>
+        </is>
       </c>
       <c r="H18" s="1" t="n"/>
       <c r="I18" s="1" t="n"/>
@@ -872,9 +867,8 @@
           <t>Budget Kosten</t>
         </is>
       </c>
-      <c r="D19" s="7">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$B$661:$B$828,'[Steuerung.xlsx]Steuerung'!$F$10)=0,"n.a.",INDEX('[D Projekte.xlsx]D Projekte'!$I$661:$I$828,MATCH('[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$661:$B$828,0)))</f>
-        <v/>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E19" s="1" t="n"/>
       <c r="F19" s="1" t="n"/>
@@ -978,17 +972,14 @@
       <c r="C24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C24)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C24))</f>
-        <v/>
-      </c>
-      <c r="E24" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C24,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C24,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F24" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C24,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C24,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D24" s="6" t="n">
+        <v>-37078.80000000005</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="G24" s="1" t="n"/>
       <c r="H24" s="1" t="n"/>
@@ -1006,17 +997,14 @@
       <c r="C25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C25)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C25))</f>
-        <v/>
-      </c>
-      <c r="E25" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C25,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C25,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F25" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C25,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C25,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D25" s="6" t="n">
+        <v>-1315900.49</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>298</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="G25" s="1" t="n"/>
       <c r="H25" s="1" t="n"/>
@@ -1034,17 +1022,14 @@
       <c r="C26" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C26)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C26))</f>
-        <v/>
-      </c>
-      <c r="E26" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C26,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C26,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F26" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C26,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C26,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D26" s="6" t="n">
+        <v>-81007.93000000005</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>22</v>
       </c>
       <c r="G26" s="1" t="n"/>
       <c r="H26" s="1" t="n"/>
@@ -1062,17 +1047,14 @@
       <c r="C27" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C27)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C27))</f>
-        <v/>
-      </c>
-      <c r="E27" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C27,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C27,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F27" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C27,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C27,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D27" s="6" t="n">
+        <v>-82182.98999999999</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>400.75</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="G27" s="1" t="n"/>
       <c r="H27" s="1" t="n"/>
@@ -1090,17 +1072,14 @@
       <c r="C28" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C28)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C28))</f>
-        <v/>
-      </c>
-      <c r="E28" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C28,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C28,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F28" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C28,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C28,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D28" s="6" t="n">
+        <v>-55626.52000000002</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>223.75</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="G28" s="1" t="n"/>
       <c r="H28" s="1" t="n"/>
@@ -1118,17 +1097,14 @@
       <c r="C29" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D29" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C29)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C29))</f>
-        <v/>
-      </c>
-      <c r="E29" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C29,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C29,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F29" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C29,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C29,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D29" s="6" t="n">
+        <v>-56310.82000000002</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>22</v>
       </c>
       <c r="G29" s="1" t="n"/>
       <c r="H29" s="1" t="n"/>
@@ -1146,17 +1122,14 @@
       <c r="C30" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D30" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C30)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C30))</f>
-        <v/>
-      </c>
-      <c r="E30" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C30,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C30,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F30" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C30,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C30,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D30" s="6" t="n">
+        <v>-89019.3</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>23</v>
       </c>
       <c r="G30" s="1" t="n"/>
       <c r="H30" s="1" t="n"/>
@@ -1174,17 +1147,14 @@
       <c r="C31" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D31" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C31)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C31))</f>
-        <v/>
-      </c>
-      <c r="E31" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C31,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C31,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F31" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C31,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C31,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D31" s="6" t="n">
+        <v>20257.7</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="G31" s="1" t="n"/>
       <c r="H31" s="1" t="n"/>
@@ -1202,17 +1172,12 @@
       <c r="C32" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D32" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C32)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C32))</f>
-        <v/>
-      </c>
-      <c r="E32" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C32,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C32,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F32" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C32,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C32,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="G32" s="1" t="n"/>
       <c r="H32" s="1" t="n"/>
@@ -1230,18 +1195,9 @@
       <c r="C33" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C33)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C33))</f>
-        <v/>
-      </c>
-      <c r="E33" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C33,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C33,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F33" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C33,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C33,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
       <c r="G33" s="1" t="n"/>
       <c r="H33" s="1" t="n"/>
       <c r="I33" s="1" t="n"/>
@@ -1258,18 +1214,9 @@
       <c r="C34" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D34" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C34)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C34,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C34,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F34" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C34,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C34,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
       <c r="G34" s="1" t="n"/>
       <c r="H34" s="1" t="n"/>
       <c r="I34" s="1" t="n"/>
@@ -1286,18 +1233,9 @@
       <c r="C35" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D35" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C35)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$H$1420:$H$4919,'[D Projekte.xlsx]D Projekte'!$A$1420:$A$4919,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$G$1420:$G$4919,C35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C35,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$158:$G$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C35,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="F35" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C35,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"",SUMIFS('[D Projekte.xlsx]D Projekte'!$I$158:$I$349,'[D Projekte.xlsx]D Projekte'!$C$158:$C$349,'[Steuerung.xlsx]Steuerung'!$F$10,'[D Projekte.xlsx]D Projekte'!$B$158:$B$349,C35,'[D Projekte.xlsx]D Projekte'!$A$158:$A$349,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
       <c r="G35" s="1" t="n"/>
       <c r="H35" s="1" t="n"/>
       <c r="I35" s="1" t="n"/>
@@ -1733,6 +1671,8 @@
       <c r="N60" s="1" t="n"/>
       <c r="O60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
